--- a/data_in_templates/input_parameter_temp.xlsx
+++ b/data_in_templates/input_parameter_temp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mohammedfaran/Desktop/python_models/ReactorModels/data_in_templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim/Desktop/pfas_modeling/reactormodels/data_in_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BC7D08-53F1-5F46-A0C5-670605EC8303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6975F1-0613-9044-A2CD-ADCA349F562A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="500" windowWidth="27860" windowHeight="17500" xr2:uid="{8FC1EBE6-09F5-E544-BEAB-0C438D750464}"/>
+    <workbookView xWindow="940" yWindow="680" windowWidth="27860" windowHeight="17500" activeTab="1" xr2:uid="{8FC1EBE6-09F5-E544-BEAB-0C438D750464}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
@@ -111,9 +111,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>diffusion</t>
-  </si>
-  <si>
     <t>molecular_weight</t>
   </si>
   <si>
@@ -175,6 +172,9 @@
   </si>
   <si>
     <t>chemical 7</t>
+  </si>
+  <si>
+    <t>axial_diffusion</t>
   </si>
 </sst>
 </file>
@@ -330,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -386,9 +386,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -734,12 +731,12 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -775,7 +772,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -784,7 +781,7 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -793,7 +790,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -820,7 +817,7 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -847,7 +844,7 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -856,16 +853,16 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -892,10 +889,10 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -904,10 +901,10 @@
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -919,7 +916,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -928,7 +925,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -937,7 +934,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -980,25 +977,25 @@
         <v>23</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>25</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>26</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>29</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="10"/>
@@ -1021,7 +1018,7 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="7"/>
@@ -1033,7 +1030,7 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1063,7 +1060,7 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1093,7 +1090,7 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1123,7 +1120,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1153,7 +1150,7 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1183,7 +1180,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1212,7 +1209,7 @@
       <c r="Z8" s="11"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A9" s="24"/>
+      <c r="A9" s="10"/>
       <c r="C9" s="11"/>
       <c r="D9" s="19"/>
       <c r="E9" s="11"/>
